--- a/r5-TC-FHIR-AG-Scheduling-R5-16-profile-notes/StructureDefinition-at-scheduling-healthcareservice.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-16-profile-notes/StructureDefinition-at-scheduling-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T07:38:32+00:00</t>
+    <t>2025-03-21T10:12:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
